--- a/data/pack/eu/arroz.xlsx
+++ b/data/pack/eu/arroz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K954"/>
+  <dimension ref="A1:K955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27136,7 +27136,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>292.51</v>
+        <v>290.02</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>292.39</v>
+        <v>289.56</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>292.37</v>
+        <v>289.46</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>292.42</v>
+        <v>289.68</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>289.71</v>
+        <v>292.43</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>289.7</v>
+        <v>292.43</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -52904,6 +52904,61 @@
         </is>
       </c>
       <c r="K954" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>arroz</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Arroz</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E955" t="n">
+        <v>314.29</v>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -53007,7 +53062,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -53018,7 +53073,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="9">
@@ -53113,7 +53168,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
